--- a/assets/Question.xlsx
+++ b/assets/Question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\July\Webpage\gift_app\gift_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFD8B30-A171-402F-B185-659E93BD804C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ADD985-4802-4F21-B9C5-5565FD79BF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7E08EA8-8B01-4178-B063-30CD87AB5CF6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Question</t>
   </si>
@@ -45,12 +45,6 @@
     <t>Answer 2</t>
   </si>
   <si>
-    <t>Who is this gift from?</t>
-  </si>
-  <si>
-    <t>Chanda Mama</t>
-  </si>
-  <si>
     <t>Pani puri</t>
   </si>
   <si>
@@ -72,9 +66,6 @@
     <t>Mumma</t>
   </si>
   <si>
-    <t>Mommy</t>
-  </si>
-  <si>
     <t>Bhai</t>
   </si>
   <si>
@@ -172,6 +163,75 @@
   </si>
   <si>
     <t>Mira</t>
+  </si>
+  <si>
+    <t>Road</t>
+  </si>
+  <si>
+    <t>You made me feel jealous for the first time by using this girl's name</t>
+  </si>
+  <si>
+    <t>Chunmun</t>
+  </si>
+  <si>
+    <t>Chetna</t>
+  </si>
+  <si>
+    <t>When you dropped me home first time, what did you saw in my home?</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>A Cat</t>
+  </si>
+  <si>
+    <t>Where was the breaking point?</t>
+  </si>
+  <si>
+    <t>Nerul</t>
+  </si>
+  <si>
+    <t>Neral</t>
+  </si>
+  <si>
+    <t>What did you say you have brought for me when I first came back from Mumbai?</t>
+  </si>
+  <si>
+    <t>Shoe</t>
+  </si>
+  <si>
+    <t>Sandal</t>
+  </si>
+  <si>
+    <t>What was the flavour of the cake we had on 2nd Saturday night?</t>
+  </si>
+  <si>
+    <t>Butterscotch</t>
+  </si>
+  <si>
+    <t>Choco butterscotch</t>
+  </si>
+  <si>
+    <t>Butterscotch Chocolate</t>
+  </si>
+  <si>
+    <t>Who is Audit's Faculty?</t>
+  </si>
+  <si>
+    <t>Ankush Chirimar</t>
+  </si>
+  <si>
+    <t>Ankush</t>
+  </si>
+  <si>
+    <t>Chirimar</t>
+  </si>
+  <si>
+    <t>What is one thing our principal does not like?</t>
+  </si>
+  <si>
+    <t>Foreplay</t>
   </si>
 </sst>
 </file>
@@ -523,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E1F31A-66EA-4229-866F-9C2CFF4AF760}">
-  <dimension ref="B1:G15"/>
+  <dimension ref="B1:G21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="87.77734375" bestFit="1" customWidth="1"/>
@@ -543,81 +603,81 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+      <c r="E2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -628,35 +688,35 @@
       <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
@@ -666,16 +726,19 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
@@ -691,13 +754,82 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
